--- a/website/examples/example_odk_attestation.create_Fingerprint.xlsx
+++ b/website/examples/example_odk_attestation.create_Fingerprint.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R35f97ae91b5e4c31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8b5a12503919417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R7dbfe10b63a149f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rbe0229659e7243d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rcc15a0789ad5481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R4239aa91b56646b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -615,7 +615,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='attestation.create',entity_type='participant',entity_id=${participant_id},subject_id=${participant_id},operator_id=${operator_id_input},input_study_id='researchos_attestation_test',input_event_type='form_submission',input_event_payload_hash=${event_payload_hash},input_verification_method='Fingerprint',input_trusted_timestamp=${timestamp_policy},return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='attestation.create',entity_type='participant',entity_id=${participant_id},subject_id=${participant_id},operator_id=${operator_id_input},input_study_id='methodmesh_attestation_test',input_event_type='form_submission',input_event_payload_hash=${event_payload_hash},input_verification_method='Fingerprint',input_trusted_timestamp=${timestamp_policy},return_mode='flat')</x:v>
       </x:c>
       <x:c r="J12" s="11"/>
       <x:c r="K12" s="11"/>
@@ -625,10 +625,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D13" s="11"/>
       <x:c r="E13" s="11"/>
@@ -646,10 +646,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>researchos_method_id</x:v>
+        <x:v>methodmesh_method_id</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>ResearchOS method ID</x:v>
+        <x:v>MethodMesh method ID</x:v>
       </x:c>
       <x:c r="D14" s="11"/>
       <x:c r="E14" s="11"/>
@@ -667,10 +667,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D15" s="11"/>
       <x:c r="E15" s="11"/>
